--- a/Шаблон_Пиво_А5.xlsx
+++ b/Шаблон_Пиво_А5.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2772,83 +2772,87 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Чешская Деситка</t>
+          <t>Поцелуй Фрейи</t>
         </is>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.04</v>
+        <v>0.047</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E61" s="1" t="n">
-        <v>0.1</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>светлое фильтрованное</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Лагер</t>
+          <t>Медовуха</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
+          <t>СОСТАВ: вода, цветочный мед, сахар, дрожжи</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cheshskaya_Desitka.jpg</t>
+          <t>freya.jpg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Чешское Домашнее</t>
+          <t>Кровь Валькирии</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.032</v>
+        <v>0.047</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E62" s="1" t="n">
-        <v>0.09</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>светлое фильтрованное</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Лагер</t>
+          <t>Медовуха</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
+          <t>СОСТАВ: вода, цветочный мед, вишневый сок, дрожжи</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Cheshskoe_Domashnee.jpg</t>
+          <t>krov_valkirii.jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Чешское Элитное</t>
+          <t>Плата Мимира</t>
         </is>
       </c>
       <c r="C63" s="1" t="n">
@@ -2859,139 +2863,255 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E63" s="1" t="n">
-        <v>0.12</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>светлое фильтрованное</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Лагер</t>
+          <t>Медовуха</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
+          <t>СОСТАВ: вода, цвет. мед, сок голубики, экст. ореха, дрожжи</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Cheshskoe_Elitnoe.jpg</t>
+          <t>plata_mimira.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Чешская Деситка</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>светлое фильтрованное</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Лагер</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Cheshskaya_Desitka.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="1" s="8">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Чешское Домашнее</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>светлое фильтрованное</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Лагер</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Cheshskoe_Domashnee.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="1" s="8">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Чешское Элитное</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>светлое фильтрованное</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Лагер</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Cheshskoe_Elitnoe.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Schneider Weisse TAP 1 Hefeweissbier Naturtrub</t>
         </is>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C67" s="1" t="n">
         <v>0.049</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D67" t="n">
         <v>13</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E67" s="1" t="n">
         <v>0.113</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>светлое нефильтрованное</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Weissbier</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>СОСТАВ: вода, солод пивовар. яч.; пшен., хмель, дрожжи</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Schneider_Weisse_TAP_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="65" customFormat="1" s="8">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>Алтайский ГОСТ 1л</t>
         </is>
       </c>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="9" t="n">
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="n">
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
         <v>0.11</v>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>светлое фильтрованное</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Лагер</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>Altajskij_GOST.jpg</t>
         </is>
       </c>
     </row>
-    <row r="66" customFormat="1" s="8">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>Алтайский ГОСТ 1.5л</t>
         </is>
       </c>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="9" t="n">
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="n">
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
         <v>0.11</v>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>светлое фильтрованное</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Лагер</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>СОСТАВ: вода, солод пив. яч., хмель, дрожжи</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>Altajskij_GOST.jpg</t>
         </is>
